--- a/data/trans_orig/IP21B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Provincia-trans_orig.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45377</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54722</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,46%</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
